--- a/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-soil.xlsx
+++ b/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-soil.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-19-pig-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B7452C-C9FE-47B7-9025-4F187538DCAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EF0376-2D14-4FEF-9C6D-17F707E96C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Field Water content" sheetId="1" r:id="rId1"/>
+    <sheet name="Water content" sheetId="1" r:id="rId1"/>
     <sheet name="Packed soils" sheetId="2" r:id="rId2"/>
     <sheet name="soil pH" sheetId="3" r:id="rId3"/>
     <sheet name="Soil TAN" sheetId="4" r:id="rId4"/>
@@ -68,10 +68,20 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={4489860D-E65F-4BF4-81F3-9B446ED57287}</author>
     <author>tc={6EDE54FE-20B4-472F-8C86-E93C5809D78C}</author>
+    <author>tc={309308C6-4760-42FD-BADC-66D819ED43DB}</author>
   </authors>
   <commentList>
-    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{6EDE54FE-20B4-472F-8C86-E93C5809D78C}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{4489860D-E65F-4BF4-81F3-9B446ED57287}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    To reach water concentration of 19 %</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="1" shapeId="0" xr:uid="{6EDE54FE-20B4-472F-8C86-E93C5809D78C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -79,6 +89,14 @@
     Rounded to 2.8 mL</t>
       </text>
     </comment>
+    <comment ref="M5" authorId="2" shapeId="0" xr:uid="{309308C6-4760-42FD-BADC-66D819ED43DB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Within dubplicate range from the day before the experiment</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -86,10 +104,19 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={FBFC66BA-3C01-40C6-B4A3-AC3B16600579}</author>
     <author>tc={3E7317BE-A033-4FDC-A34F-45A5610D16BB}</author>
   </authors>
   <commentList>
-    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{3E7317BE-A033-4FDC-A34F-45A5610D16BB}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{FBFC66BA-3C01-40C6-B4A3-AC3B16600579}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Avg during cattle field applikation was 5.80 - weird one field sample had such a drastic increase while the other didn’t? </t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="1" shapeId="0" xr:uid="{3E7317BE-A033-4FDC-A34F-45A5610D16BB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -102,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -179,19 +206,31 @@
     <t>stdev [g]</t>
   </si>
   <si>
-    <t>water in packed soil [g]</t>
-  </si>
-  <si>
     <t>Field water content (02-02-2026) [g(water) / g(soil)]</t>
   </si>
   <si>
-    <t>Packed water conent (02-02-2026) [g(water/g(soil)</t>
-  </si>
-  <si>
     <t>2 field samples used as dublicates</t>
   </si>
   <si>
     <t>TAN-concentration bellow meassurable range</t>
+  </si>
+  <si>
+    <t>Packed water content (18-02-2026) [g(water) / g(dry))</t>
+  </si>
+  <si>
+    <t>Packed water conent (02-02-2026) [g(water/g(dry)</t>
+  </si>
+  <si>
+    <t>water in packed soil [g] (02-02)</t>
+  </si>
+  <si>
+    <t>Water in packed soil  (18-02)</t>
+  </si>
+  <si>
+    <t>Added water  [g]</t>
+  </si>
+  <si>
+    <t>water content [g(water) / g soil]</t>
   </si>
 </sst>
 </file>
@@ -550,14 +589,23 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="L1" dT="2026-02-19T07:52:01.64" personId="{2FA62AA0-6EA6-4B43-9405-0CBD5D0BA949}" id="{4489860D-E65F-4BF4-81F3-9B446ED57287}">
+    <text>To reach water concentration of 19 %</text>
+  </threadedComment>
   <threadedComment ref="N2" dT="2026-02-18T14:22:06.86" personId="{2FA62AA0-6EA6-4B43-9405-0CBD5D0BA949}" id="{6EDE54FE-20B4-472F-8C86-E93C5809D78C}">
     <text>Rounded to 2.8 mL</text>
   </threadedComment>
+  <threadedComment ref="M5" dT="2026-02-19T07:51:18.08" personId="{2FA62AA0-6EA6-4B43-9405-0CBD5D0BA949}" id="{309308C6-4760-42FD-BADC-66D819ED43DB}">
+    <text>Within dubplicate range from the day before the experiment</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C3" dT="2026-02-22T14:13:04.49" personId="{2FA62AA0-6EA6-4B43-9405-0CBD5D0BA949}" id="{FBFC66BA-3C01-40C6-B4A3-AC3B16600579}">
+    <text xml:space="preserve">Avg during cattle field applikation was 5.80 - weird one field sample had such a drastic increase while the other didn’t? </text>
+  </threadedComment>
   <threadedComment ref="A4" dT="2026-02-18T14:17:02.32" personId="{2FA62AA0-6EA6-4B43-9405-0CBD5D0BA949}" id="{3E7317BE-A033-4FDC-A34F-45A5610D16BB}">
     <text>Done by Marzieh - not on the same day!</text>
   </threadedComment>
@@ -771,6 +819,24 @@
       <c r="C10">
         <v>4.2889999999999997</v>
       </c>
+      <c r="D10">
+        <v>112.913</v>
+      </c>
+      <c r="E10">
+        <f>D10-C10</f>
+        <v>108.624</v>
+      </c>
+      <c r="F10">
+        <v>92.739000000000004</v>
+      </c>
+      <c r="G10">
+        <f>E10-F10</f>
+        <v>15.884999999999991</v>
+      </c>
+      <c r="H10" s="2">
+        <f>G10/F10</f>
+        <v>0.17128716074143555</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
@@ -779,6 +845,24 @@
       <c r="C11">
         <v>4.2750000000000004</v>
       </c>
+      <c r="D11">
+        <v>74.376999999999995</v>
+      </c>
+      <c r="E11">
+        <f t="shared" ref="E11:E13" si="3">D11-C11</f>
+        <v>70.10199999999999</v>
+      </c>
+      <c r="F11">
+        <v>62.08</v>
+      </c>
+      <c r="G11">
+        <f t="shared" ref="G11:G13" si="4">E11-F11</f>
+        <v>8.0219999999999914</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" ref="H11:H13" si="5">G11/F11</f>
+        <v>0.12922036082474214</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
@@ -787,6 +871,24 @@
       <c r="C12">
         <v>4.2729999999999997</v>
       </c>
+      <c r="D12">
+        <v>54.822000000000003</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="3"/>
+        <v>50.549000000000007</v>
+      </c>
+      <c r="F12">
+        <v>47.103999999999999</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="4"/>
+        <v>3.4450000000000074</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="5"/>
+        <v>7.3136039402174072E-2</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
@@ -794,6 +896,24 @@
       </c>
       <c r="C13">
         <v>4.2869999999999999</v>
+      </c>
+      <c r="D13">
+        <v>54.572000000000003</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>50.285000000000004</v>
+      </c>
+      <c r="F13">
+        <v>46.856999999999999</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="4"/>
+        <v>3.4280000000000044</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="5"/>
+        <v>7.315875963036482E-2</v>
       </c>
     </row>
   </sheetData>
@@ -810,15 +930,15 @@
     <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -830,10 +950,10 @@
         <v>14</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F1" t="s">
         <v>15</v>
@@ -848,7 +968,7 @@
         <v>24</v>
       </c>
       <c r="K1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L1" t="s">
         <v>19</v>
@@ -868,11 +988,11 @@
         <v>100</v>
       </c>
       <c r="C2" s="2">
-        <f>'Field Water content'!H2</f>
+        <f>'Water content'!H2</f>
         <v>0.19022510021584965</v>
       </c>
       <c r="D2" s="2">
-        <f>'Field Water content'!H5</f>
+        <f>'Water content'!H5</f>
         <v>0.12269215492831417</v>
       </c>
       <c r="F2" s="2">
@@ -913,25 +1033,35 @@
         <v>1.45</v>
       </c>
       <c r="C3" s="2">
-        <f>'Field Water content'!H3</f>
+        <f>'Water content'!H3</f>
         <v>0.18909675079027832</v>
       </c>
       <c r="D3" s="2">
-        <f>'Field Water content'!H6</f>
+        <f>'Water content'!H6</f>
         <v>0.11472410740631449</v>
       </c>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>1.44</v>
       </c>
       <c r="C4" s="2">
-        <f>'Field Water content'!H4</f>
+        <f>'Water content'!H4</f>
         <v>0.19148936170212763</v>
       </c>
       <c r="D4" s="2">
-        <f>'Field Water content'!H7</f>
+        <f>'Water content'!H7</f>
         <v>0.11078899586505737</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -945,6 +1075,18 @@
       <c r="E5" t="s">
         <v>13</v>
       </c>
+      <c r="K5">
+        <f>F2*D9</f>
+        <v>10.220000000000001</v>
+      </c>
+      <c r="L5" s="3">
+        <f>M2</f>
+        <v>11.011457576125917</v>
+      </c>
+      <c r="M5" s="3">
+        <f>(K5+L5)/(F2-K5)</f>
+        <v>0.15636660462605625</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
@@ -967,10 +1109,16 @@
       <c r="A8" s="4">
         <v>1.44</v>
       </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>1.6</v>
+      </c>
+      <c r="D9">
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1070,17 +1218,53 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B116D794-955B-45EB-993C-44A4506448A7}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="F2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G2">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>1.2</v>
+      </c>
+      <c r="G3">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>2.1</v>
+      </c>
+      <c r="G4">
+        <v>1.0109999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G5">
+        <v>0.97699999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-soil.xlsx
+++ b/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-soil.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-19-pig-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EF0376-2D14-4FEF-9C6D-17F707E96C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68A62A9-F5A5-4BD8-83E0-F0BB832A1559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Water content" sheetId="1" r:id="rId1"/>
@@ -240,19 +240,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -886,7 +880,7 @@
         <v>3.4450000000000074</v>
       </c>
       <c r="H12" s="2">
-        <f t="shared" si="5"/>
+        <f>G12/F12</f>
         <v>7.3136039402174072E-2</v>
       </c>
     </row>

--- a/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-soil.xlsx
+++ b/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-soil.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-19-pig-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68A62A9-F5A5-4BD8-83E0-F0BB832A1559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1392533-15A4-46D0-BFCF-FDCF230743E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Water content" sheetId="1" r:id="rId1"/>
